--- a/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regSummary_ASX300_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regSummary_ASX300_Real_Estate.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.292707877841557</v>
+        <v>1.135479736112159</v>
       </c>
       <c r="H2" t="n">
-        <v>4.720673415920713</v>
+        <v>4.760506629179263</v>
       </c>
       <c r="I2" t="n">
         <v>-7.641550815508549</v>
@@ -545,19 +545,19 @@
         <v>13.2283841318109</v>
       </c>
       <c r="K2" t="n">
-        <v>37.62376237623762</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1238193323787008</v>
+        <v>0.1109077722028314</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01998150231082008</v>
+        <v>0.01560353545881421</v>
       </c>
       <c r="P2" t="n">
         <v>0.3138540007036315</v>
@@ -603,7 +603,7 @@
         <v>11.9534070082495</v>
       </c>
       <c r="K3" t="n">
-        <v>12.87128712871287</v>
+        <v>12.74509803921569</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>5.99996918574318</v>
       </c>
       <c r="K4" t="n">
-        <v>4.95049504950495</v>
+        <v>4.901960784313726</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>14.1184473609332</v>
       </c>
       <c r="K5" t="n">
-        <v>44.55445544554455</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
